--- a/piratas_e_cavaleiros/habilidades.xlsx
+++ b/piratas_e_cavaleiros/habilidades.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25590" windowHeight="10400"/>
+    <workbookView windowWidth="25600" windowHeight="10400"/>
   </bookViews>
   <sheets>
     <sheet name="habilidades" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="194">
   <si>
     <t>Classe</t>
   </si>
@@ -68,7 +68,7 @@
     <t>Em vez de Esquivar, rola o dano da arma contra o atque do inimigo mitigando o dano equivalenet ao ataque.(funciona apenas contra armas brancas com lamina)</t>
   </si>
   <si>
-    <t>Reduz dado igaul ao dano da arma</t>
+    <t>Reduz dado igaul ao dano rolado da arma</t>
   </si>
   <si>
     <t>-</t>
@@ -80,13 +80,13 @@
     <t>Se inimigo errar o ataque em você, faça um ataque nele imediatamente.</t>
   </si>
   <si>
-    <t>Dano normal da arma</t>
+    <t>Pode atacar um inimigo se ele errar um ataque em voce</t>
   </si>
   <si>
     <t>Postura de Defesa</t>
   </si>
   <si>
-    <t>Ação Principal</t>
+    <t>3 Vigor + Ação de Preparação</t>
   </si>
   <si>
     <t>Abdica do ataque para focar em defesa, entrando em uma posturade Guarda  (Guarda vira 10+Armadura+DEX.)</t>
@@ -98,13 +98,13 @@
     <t>ataque preciso</t>
   </si>
   <si>
-    <t>Ação principal com preparação</t>
+    <t>Ação de Preparação</t>
   </si>
   <si>
     <t>em um turno pode se preparar para desferir um ataque com vantagem ignorando a aramdura do inimigo sua defesa diminui em 2 (8 + armadura) se for atacado perde a preparação</t>
   </si>
   <si>
-    <t>ignora a armadura do alvo no teste e no dano</t>
+    <t>ignora a armadura do alvo no teste e no dano (a CA fica apenas com bonus de raça e a CA base de 10)</t>
   </si>
   <si>
     <t>P. Classe</t>
@@ -116,46 +116,499 @@
     <t xml:space="preserve"> utilizando da sua agilidade pode se mover atacar e se mover de novo, otimo para sair da distancia dos ataques </t>
   </si>
   <si>
-    <t>pode se mover apos atacar</t>
+    <t>pode se mover apos atacar se não tiver restrição e sobrar movimentação</t>
   </si>
   <si>
     <t>golpe de oportunidade</t>
   </si>
   <si>
-    <t>1 vigor</t>
+    <t>2 vigor</t>
   </si>
   <si>
     <t xml:space="preserve">faz um golpe rapido no ponto cego do inimigo podendo acertar um ponto vital com mais facilidade </t>
   </si>
   <si>
-    <t>pode tirara um critico com 18 sem ser natural</t>
+    <t>aumenta su taxa de critico em +1 sem ser natural</t>
   </si>
   <si>
     <t>Arquétipo</t>
   </si>
   <si>
-    <t>Reduz 2 dados da arma + Atributo</t>
-  </si>
-  <si>
-    <t>Arquétipo X</t>
-  </si>
-  <si>
-    <t>Mago</t>
-  </si>
-  <si>
-    <t>Magia</t>
-  </si>
-  <si>
-    <t>Raio de Fogo</t>
-  </si>
-  <si>
-    <t>1 Mana + Principal</t>
-  </si>
-  <si>
-    <t>Lança fogo pelas mãos num alvo até 9m.</t>
-  </si>
-  <si>
-    <t>1d10 Fogo</t>
+    <t>Guarda Nobre</t>
+  </si>
+  <si>
+    <t>Escola inspirada na esgrima clássica: exige preparação prévia através de guardas rígidas, mas transforma isso em defesas e ataques muito poderosos, dando mais opções ao espadachim.</t>
+  </si>
+  <si>
+    <t>Enquanto em uma Postura, a postura pode ser mantida por 1 turno adicional sem nova preparação.</t>
+  </si>
+  <si>
+    <t>Escola da agua</t>
+  </si>
+  <si>
+    <t>Escola inspirada na esgrima das terras do leste: movimentação rápida, estocadas certeiras e golpes em sequência, com a precisão como maior arma, não a força bruta.</t>
+  </si>
+  <si>
+    <t>Ao errar um ataque pode gastar 1 Vigor para repeti-lo imediatamente.</t>
+  </si>
+  <si>
+    <t>Escola Pêndulo Partido</t>
+  </si>
+  <si>
+    <t>1 Vigor</t>
+  </si>
+  <si>
+    <t>Escola inspirada na esgrima das terras do norte: controle do fluxo do combate através da manipulação das armas do oponente, rasteiras, desarmamento e quebra de posturas.</t>
+  </si>
+  <si>
+    <t>Quando um inimigo erra um ataque corpo a corpo contra você ao gastar sua reação e 1 de vigor pode dar um golpe desarmado nele.</t>
+  </si>
+  <si>
+    <t>Guarda Baixa</t>
+  </si>
+  <si>
+    <t>1 Vigor + Ação de Preparação</t>
+  </si>
+  <si>
+    <t>Entra em uma postura que aumenta o ataque mas deixa a defesa mais dificil.</t>
+  </si>
+  <si>
+    <t>Próximos ataques causam +1d6 a cada 2 niveis de dano, mas a CA diminui em -2  e não se pode bloquear até sair da postura.</t>
+  </si>
+  <si>
+    <t>Retorno de Guarda</t>
+  </si>
+  <si>
+    <t>Reação, 1 Vigor</t>
+  </si>
+  <si>
+    <t>Se recupera rapidamente de uma defesa.</t>
+  </si>
+  <si>
+    <t>Pode gastar 1 de vigor para recuperar a reação.</t>
+  </si>
+  <si>
+    <t>Fluidez das Guardas</t>
+  </si>
+  <si>
+    <t>Você domina a transição entre guardas conhecidas.</t>
+  </si>
+  <si>
+    <t>Trocar de postura custa Vigor 2 normalmente e não exige nova Ação de Preparação se já estiver em alguma postura.</t>
+  </si>
+  <si>
+    <t>Estocada</t>
+  </si>
+  <si>
+    <t>Causa dano baseado na distancia de movimeto.</t>
+  </si>
+  <si>
+    <t>Ganha +4 de dano por metro percorrido em linha reta ate o alvo.</t>
+  </si>
+  <si>
+    <t>Passo Fantasma</t>
+  </si>
+  <si>
+    <t>Sua movimentação é tão precisa quanto uma linha em uma agulha.</t>
+  </si>
+  <si>
+    <t>Pode passar por pessoas com vantagem de furtividade +2 e em combates pernosagens medios para baixo não sao obstaculos podenso se mover normalmente.</t>
+  </si>
+  <si>
+    <t>Precisão Constante</t>
+  </si>
+  <si>
+    <t>Sua concentração afia cada golpe.</t>
+  </si>
+  <si>
+    <t>Aumenta em 1 sua faixa de crítico em ataques .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarme </t>
+  </si>
+  <si>
+    <t>1 Vigor, Ação</t>
+  </si>
+  <si>
+    <t>Você mira na arma do inimigo para a desarmar.</t>
+  </si>
+  <si>
+    <t>Teste oposto, o inimigo faz um teste de CON contra a sau DEX se falhar derruba a arma .</t>
+  </si>
+  <si>
+    <t>Manobra</t>
+  </si>
+  <si>
+    <t>Uma manobra baixa desestabiliza o oponente.</t>
+  </si>
+  <si>
+    <t>Teste de DEX conta a CON do inimigo, se passar deixa o inimigo caido e vulnerável a ataques (so vale para o mesmo tamanho ou inferior) .</t>
+  </si>
+  <si>
+    <t>Leitura de Combate</t>
+  </si>
+  <si>
+    <t>Um erro do inimigo revela seus próximos passos.</t>
+  </si>
+  <si>
+    <t>Vantagem em testes para prever/contrapor a próxima ação de um inimigo que já errou um ataque contra você neste combate, +2 em bloqueios, esquivas, ataques , contra ataques, habilidades, testes e defesa.</t>
+  </si>
+  <si>
+    <t>postura carrasco</t>
+  </si>
+  <si>
+    <t>5 vigor + Ação de Preparação</t>
+  </si>
+  <si>
+    <t>Golpe que utiliza todos os musculos do corpo para desferir um ataque devastador sem precisão ou controle, um ataque sem controle pode ser devastador para a sua arma  .</t>
+  </si>
+  <si>
+    <t>causa 3x dano da arma com -5 de vantagem para atacar (se acertar um critico o dano não é dobrado e falhas criticas danificam a arma gravemente ).</t>
+  </si>
+  <si>
+    <t>Conhecedor do ferro</t>
+  </si>
+  <si>
+    <t>Ao olhar para uma arma ou armadura sabe sua qualidade, valor, sua resistencia e até sua possivel origem/forja, como se o metal te contace sua historia.</t>
+  </si>
+  <si>
+    <t>Vantagem consegue saber bonus de dadno de um inimigo sua defesa e tem vantagens +2 em testes de reconhecer ferramentas e armaduras .</t>
+  </si>
+  <si>
+    <t>Golpe de Transição</t>
+  </si>
+  <si>
+    <t>Encerrar postura</t>
+  </si>
+  <si>
+    <t>Ao sair de uma guarda, você aproveita o impulso do movimento.</t>
+  </si>
+  <si>
+    <t>Ataque bônus imediato com vantagem +2 ao encerrar uma postura.</t>
+  </si>
+  <si>
+    <t>Sequência de Cortes</t>
+  </si>
+  <si>
+    <t>Dois cortes rápidos e leves, quase simultâneos.</t>
+  </si>
+  <si>
+    <t>Dois ataques no mesmo turno.</t>
+  </si>
+  <si>
+    <t>Fluxo da Correnteza</t>
+  </si>
+  <si>
+    <t>Você enxerga o fluxo de força dos ataques e do ambiente possibilitando guialo para onde desejar.</t>
+  </si>
+  <si>
+    <t>Vantagem +2 em testes para identificar pontos fracos na defesa do inimigo, resistencia a agarroes, derrubar inimigos , aparar*, corridas, acobracias e +1 CAR  em dialogos.</t>
+  </si>
+  <si>
+    <t>Golpe Relâmpago</t>
+  </si>
+  <si>
+    <t>2 Foco</t>
+  </si>
+  <si>
+    <t>A velocidade da esgrima do leste em seu estado mais puro, um desembanahr seguido de um ataque poderoso.</t>
+  </si>
+  <si>
+    <t>em rolagem de iniciativa pode gastar 1 de foco para virara o primeiro a atacar desferindo um golpe critico de oportunidade em um inimigo no alcance da movimentação .</t>
+  </si>
+  <si>
+    <t>Frenesi</t>
+  </si>
+  <si>
+    <t>Abre mao da defesa para entrar em uma postura de ataques e contra ataques nas brexas dadas pelos ataques dos inimigos em seu corpo .</t>
+  </si>
+  <si>
+    <t>Não gasta mais vigor para realizar açoes por até 1D6 + CON turnos podendo parar antes mas não podera mais entarar nessa postura no combate, sua CA cai para 5 + armadura (-5 de defesa base) e todo golpe que um inimigo acertar em voce pode devolver um contra ataque imediatamente.</t>
+  </si>
+  <si>
+    <t>Estilo do norte</t>
+  </si>
+  <si>
+    <t>Você ataca na abertura de seu ataque com seus punhos e pés.</t>
+  </si>
+  <si>
+    <t>Ao atacar pode rolar um segundo ataques corpo a corpo desarmado.</t>
+  </si>
+  <si>
+    <t>Controle do Confronto</t>
+  </si>
+  <si>
+    <t>Cada oponente subjugado renova seu fôlego.</t>
+  </si>
+  <si>
+    <t>Sempre que derrotar ou matar um oponenete recupera 1 ponto de Vigor.</t>
+  </si>
+  <si>
+    <t>Guarda do Vendaval</t>
+  </si>
+  <si>
+    <t>Ação secundaria</t>
+  </si>
+  <si>
+    <t>Guarda focada em mobilidade defensiva, com disparadas rapidas.</t>
+  </si>
+  <si>
+    <t>Se move em linha reta em um unico impulso que é sua Movimentação + FOR.</t>
+  </si>
+  <si>
+    <t>Guarda de Aço</t>
+  </si>
+  <si>
+    <t>1 Foco</t>
+  </si>
+  <si>
+    <t>Seu estintos durante um combate se afloram em situaçoes de risco.</t>
+  </si>
+  <si>
+    <t>pode anular o dano de um critico, o acerto se mantem mas perde os beneficios do critico.</t>
+  </si>
+  <si>
+    <t>Um com a Espada</t>
+  </si>
+  <si>
+    <t>passou tanto tempo com sua arma que ela parece uma extenção do seu corpo.</t>
+  </si>
+  <si>
+    <t>Ate tres armas nao pesão mais nada para carregalas e sua espada nao ocupa mais espaço no inventario e voce pode esatr sempre com ela .</t>
+  </si>
+  <si>
+    <t>Fluxo Constante</t>
+  </si>
+  <si>
+    <t>Cada golpe torna o próximo mais natural.</t>
+  </si>
+  <si>
+    <t>cada ataque seguido no mesmo inimigo tem +1 de vantagem para acertar (Max:5).</t>
+  </si>
+  <si>
+    <t>Reflexo do Mestre</t>
+  </si>
+  <si>
+    <t>Você responde aos ataques de forma mais natural .</t>
+  </si>
+  <si>
+    <t>Ganha +2 reaçoes no turno.</t>
+  </si>
+  <si>
+    <t>Roubo de batalha</t>
+  </si>
+  <si>
+    <t>2 Vigor</t>
+  </si>
+  <si>
+    <t>Uma arma avulsa do inimigo se torna sua em combate.</t>
+  </si>
+  <si>
+    <t>O oponente rola um teste de DEX contra a sua DEX se voce passar pode pegar um equipamento ou arma do oponete em combate.</t>
+  </si>
+  <si>
+    <t>Contorção Evasiva</t>
+  </si>
+  <si>
+    <t>Cada esquiva é uma oportunidade de reposicionamento.</t>
+  </si>
+  <si>
+    <t>Uma vez por turno, converte uma esquiva bem-sucedida em reposicionamento livre em cima da sua movimentação.</t>
+  </si>
+  <si>
+    <t>Ciclo de Domínio</t>
+  </si>
+  <si>
+    <t>Seus socos deixam marcas duradouras nos oponenentes.</t>
+  </si>
+  <si>
+    <t>A cada 3 golpes Corpo a Corpo o inimigo perde 2 de movimento se forem mirados nas pernas, ou 1 de CON se for no tronco (do numero total e nao do modificador) ou fica atordo ado por um turno se for na cabeça (Só vale para inimigos do mesmo tamanho ou menores que o espadachin).</t>
+  </si>
+  <si>
+    <t>Postura dupla</t>
+  </si>
+  <si>
+    <t>10 vigor + Ação de Preparação</t>
+  </si>
+  <si>
+    <t>Você mantém ums guarda de ataque e defesa perfeitas.</t>
+  </si>
+  <si>
+    <t>Adiciona DEX na sua defesa e melhora seu dano em 1D6 + DEX a cada dois niveis .</t>
+  </si>
+  <si>
+    <t>Resposta Fatal</t>
+  </si>
+  <si>
+    <t>Pode punir um erro fatal inimigo com um dano oportuno.</t>
+  </si>
+  <si>
+    <t>Se um inimigo tirara uma falha critica causa dano máximo x2, sem rolar dados.</t>
+  </si>
+  <si>
+    <t>Instinto do Duelista</t>
+  </si>
+  <si>
+    <t>Quando em combates um contra melhora sua eficiencia.</t>
+  </si>
+  <si>
+    <t>Se em combates solos contra um inimigo ativo no combate, ganha +5 de vantagem em todos os ataques e defesas e um uso de foco livre no combate.</t>
+  </si>
+  <si>
+    <t>Corte em lua</t>
+  </si>
+  <si>
+    <t>10 vigor</t>
+  </si>
+  <si>
+    <t>O corte definitiv da esgrima do leste.</t>
+  </si>
+  <si>
+    <t>O ataque corpo a corpo com a arma atinge todos os inimigos num cone frontal de 1,5m.</t>
+  </si>
+  <si>
+    <t>Dança das Lâminas Rápidas</t>
+  </si>
+  <si>
+    <t>6 Vigor</t>
+  </si>
+  <si>
+    <t>Uma sequência ininterrupta de cortes precisos contra um ou varios alvos.</t>
+  </si>
+  <si>
+    <t>Ate 6 ataques leves seguidos contra o mesmo alvo ou alvos diferentes ao alcance, cada um condicionado ao anterior acertar.</t>
+  </si>
+  <si>
+    <t>Instinto de Corte</t>
+  </si>
+  <si>
+    <t>A simples intensao de ataque é o necessario para que voce possa se defender</t>
+  </si>
+  <si>
+    <t>Uma vez por cena pode reagir a uma ataqeu supresa ou de oportunidade como se fosse uma esquiva com contra ataque se a esquiva for bem sucedida, sem gastar reação ou vigor.</t>
+  </si>
+  <si>
+    <t>Defesa de frenesi</t>
+  </si>
+  <si>
+    <t>3 vigor, Reação</t>
+  </si>
+  <si>
+    <t>Nenhum ataque múltiplo passa incontestado.</t>
+  </si>
+  <si>
+    <t>Pode utilizar multiplas reaçoes no mesmo turno gastando 3 de vigor por reação.</t>
+  </si>
+  <si>
+    <t>Golpe do deserto</t>
+  </si>
+  <si>
+    <t>Ação principal</t>
+  </si>
+  <si>
+    <t>O golpe final contra quem já está vulnerável.</t>
+  </si>
+  <si>
+    <t>Pode escolher finalizar um inimigo já desarmado, derrubado ou com em algum esatdu de vunerabilidade, sera um teste da sua CON contra a dele ao passar equivalente ao modificador de CON do adversario o finaliza na hoar (so vale para oponetes com o mesmo ou tamanho menos que voce) nesse estado voce fica vuneravel para ataques ganhando -2 de vantagem na defesa .</t>
+  </si>
+  <si>
+    <t>Antecipação Perfeita</t>
+  </si>
+  <si>
+    <t>Sua leitura de combate antecipa o movimento inimigo e reage automaticamente possibilitando desviar de mais ataques.</t>
+  </si>
+  <si>
+    <t>Ao esquivar e passar pode se esquivar novamente com -1 de vantagem.</t>
+  </si>
+  <si>
+    <t>Mestre Nobre</t>
+  </si>
+  <si>
+    <t>Você internalizou todas as guardas da escola.</t>
+  </si>
+  <si>
+    <t>A preparação para utilizar as posturas agora dura 5 turnos e pode trocar entra elas avontade .</t>
+  </si>
+  <si>
+    <t>Guarda Absoluta</t>
+  </si>
+  <si>
+    <t>O ápice da defesa : um único movimento anula qualquer ameaça.</t>
+  </si>
+  <si>
+    <t>Anula completamente um ataque (incluindo efeitos especiais) .</t>
+  </si>
+  <si>
+    <t>Legado da Escola Nobre</t>
+  </si>
+  <si>
+    <t>10 Vigor + Ação de Preparação</t>
+  </si>
+  <si>
+    <t>A postura da alta nobreza utilizada pelos altos reis , lideres de revoluçoes e  o mais antigos mestres da arte da espada das terras medias.</t>
+  </si>
+  <si>
+    <t>Nessa postura pode contra atacar qualquer ataque com um critico certeiro sem rolar dados(mas ela so dura um turno independente do dano e a utilizara ela se desfaz presisando gastar e preparar ela de novo a cada turno) .</t>
+  </si>
+  <si>
+    <t>Mestre do Corte Veloz</t>
+  </si>
+  <si>
+    <t>Você se tornou a lâmina, não quem a empunha.</t>
+  </si>
+  <si>
+    <t>Faixa de crítico aumenta permanentemente em +2 (soma-se a outros bônus de faixa de crítico) .</t>
+  </si>
+  <si>
+    <t>Golpe Definitivo</t>
+  </si>
+  <si>
+    <t>3 Foco</t>
+  </si>
+  <si>
+    <t>Um único corte com precisao e velocidade maxima , dizem que pode acertar um raio.</t>
+  </si>
+  <si>
+    <t>Role um ataque com +5 de vantagem se acertar ele dara x4 o dano.</t>
+  </si>
+  <si>
+    <t>Legado da Escola da agua</t>
+  </si>
+  <si>
+    <t>Sua disciplina reduz o peso da lamina e o esforço dos ataques.</t>
+  </si>
+  <si>
+    <t>ganha tres ataques por turno e duas reaçoes.</t>
+  </si>
+  <si>
+    <t>Mestre do Fluxo Selvagem</t>
+  </si>
+  <si>
+    <t>A luta nunca sai do seu controle.</t>
+  </si>
+  <si>
+    <t>Você nunca pode ser desarmado, não tem desvantagem em ataques derrubados , em terreno dificil ou com algum status negativo.</t>
+  </si>
+  <si>
+    <t>Controle Total do Combate</t>
+  </si>
+  <si>
+    <t>4 Foco</t>
+  </si>
+  <si>
+    <t>Você dita completamente o ritmo da luta.</t>
+  </si>
+  <si>
+    <t>Nesse combate voce tem +5 de vantagem na esquiva, e pode se posicionar onde quiser independentes dos obstaculos(exceto lugares altos , dificeis de subir e paredes sem local para passar).</t>
+  </si>
+  <si>
+    <t>Legado da Escola do pêndulo</t>
+  </si>
+  <si>
+    <t>Sua maestria torna suas reações quase instintivas com o seu corpo.</t>
+  </si>
+  <si>
+    <t>Tem reaçoes infinitas de contra ataques desarmados corpo a corpo.</t>
   </si>
 </sst>
 </file>
@@ -168,10 +621,18 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -321,12 +782,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor theme="9" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor theme="9" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -515,12 +1000,123 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="18">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -641,145 +1237,244 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1314,272 +2009,1447 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="10.8" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="5.9" customWidth="1"/>
+    <col min="2" max="2" width="5.9" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.2" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="115.9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="33.2" style="2" customWidth="1"/>
+    <col min="6" max="6" width="115.9" style="2" customWidth="1"/>
+    <col min="7" max="7" width="33.2" style="3" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="26" spans="1:8">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
+    <row r="3" ht="26" spans="1:8">
+      <c r="A3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="17">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="21" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:8">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="26" spans="1:8">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
+    <row r="5" ht="39" spans="1:8">
+      <c r="A5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="17">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
+    <row r="6" ht="26" spans="1:8">
+      <c r="A6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="26" spans="1:8">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="17">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
+    <row r="8" ht="39" spans="1:8">
+      <c r="A8" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="23">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="H8" t="s">
+      <c r="D8" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
+      <c r="F8" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="26" spans="1:8">
+      <c r="A9" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="27">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D9"/>
-      <c r="E9" t="s">
+      <c r="D9" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="2" t="s">
+      <c r="F9" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="52" spans="1:8">
+      <c r="A10" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="23">
+        <v>3</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" ht="52" spans="1:8">
+      <c r="A11" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="27">
+        <v>4</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="12" ht="26" spans="1:8">
+      <c r="A12" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="23">
+        <v>4</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="52" spans="1:8">
+      <c r="A13" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" ht="26" spans="1:8">
+      <c r="A14" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="23">
+        <v>4</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="1" t="s">
+    </row>
+    <row r="15" ht="65" spans="1:8">
+      <c r="A15" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="27">
+        <v>4</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" ht="26" spans="1:8">
+      <c r="A16" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="23">
+        <v>4</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" ht="39" spans="1:8">
+      <c r="A17" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="27">
+        <v>4</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H26" t="s">
+    </row>
+    <row r="18" ht="52" spans="1:8">
+      <c r="A18" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="23">
+        <v>4</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" ht="78" spans="1:8">
+      <c r="A19" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="27">
+        <v>4</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="28" t="s">
         <v>14</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" ht="65" spans="1:8">
+      <c r="A20" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="23">
+        <v>5</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" ht="52" spans="1:8">
+      <c r="A21" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="27">
+        <v>5</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" ht="26" spans="1:8">
+      <c r="A22" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="23">
+        <v>5</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" ht="26" spans="1:8">
+      <c r="A23" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="27">
+        <v>5</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" ht="65" spans="1:8">
+      <c r="A24" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="23">
+        <v>5</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" ht="65" spans="1:8">
+      <c r="A25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="27">
+        <v>5</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" ht="117" spans="1:8">
+      <c r="A26" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="23">
+        <v>5</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" ht="39" spans="1:8">
+      <c r="A27" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="27">
+        <v>5</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" ht="39" spans="1:8">
+      <c r="A28" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="23">
+        <v>5</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" ht="39" spans="1:8">
+      <c r="A29" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="27">
+        <v>6</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" ht="39" spans="1:8">
+      <c r="A30" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="23">
+        <v>6</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H30" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" ht="52" spans="1:8">
+      <c r="A31" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="27">
+        <v>6</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" ht="52" spans="1:8">
+      <c r="A32" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="30">
+        <v>6</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="H32" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" ht="39" spans="1:8">
+      <c r="A33" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="27">
+        <v>6</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" s="29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" ht="26" spans="1:8">
+      <c r="A34" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="23">
+        <v>6</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" ht="52" spans="1:8">
+      <c r="A35" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="27">
+        <v>6</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" ht="52" spans="1:8">
+      <c r="A36" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="23">
+        <v>6</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" ht="117" spans="1:8">
+      <c r="A37" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="27">
+        <v>6</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" ht="39" spans="1:8">
+      <c r="A38" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="23">
+        <v>7</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" ht="39" spans="1:8">
+      <c r="A39" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="27">
+        <v>7</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="H39" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" ht="65" spans="1:8">
+      <c r="A40" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="23">
+        <v>7</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G40" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="H40" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" ht="39" spans="1:8">
+      <c r="A41" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="27">
+        <v>7</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="G41" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="H41" s="29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" ht="52" spans="1:8">
+      <c r="A42" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="23">
+        <v>7</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G42" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="H42" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" ht="65" spans="1:8">
+      <c r="A43" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="27">
+        <v>7</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="H43" s="29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" ht="39" spans="1:8">
+      <c r="A44" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="23">
+        <v>7</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="G44" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="H44" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" ht="143" spans="1:8">
+      <c r="A45" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="27">
+        <v>7</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="G45" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" ht="39" spans="1:8">
+      <c r="A46" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="23">
+        <v>7</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="G46" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="H46" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" ht="39" spans="1:8">
+      <c r="A47" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="27">
+        <v>8</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="G47" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="H47" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" ht="26" spans="1:8">
+      <c r="A48" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="23">
+        <v>8</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="G48" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="H48" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" ht="91" spans="1:8">
+      <c r="A49" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="27">
+        <v>8</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" ht="39" spans="1:8">
+      <c r="A50" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="23">
+        <v>8</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="G50" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" ht="26" spans="1:8">
+      <c r="A51" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="27">
+        <v>8</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="G51" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="H51" s="29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" ht="26" spans="1:8">
+      <c r="A52" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="23">
+        <v>8</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="H52" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" ht="52" spans="1:8">
+      <c r="A53" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="27">
+        <v>8</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="G53" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" ht="78" spans="1:8">
+      <c r="A54" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="23">
+        <v>8</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="H54" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" ht="39" spans="1:8">
+      <c r="A55" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="33">
+        <v>8</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="E55" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="H55" s="35" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
